--- a/assets/r04/sheets/空白敵人角色卡.xlsx
+++ b/assets/r04/sheets/空白敵人角色卡.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="空白敵人角色卡" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,18 +26,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <color rgb="002B5797"/>
-      <sz val="14"/>
+      <sz val="16"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Microsoft JhengHei"/>
       <b val="1"/>
-      <sz val="11"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft JhengHei"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -49,16 +58,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002B5797"/>
+        <fgColor rgb="00D9E2F3"/>
+        <bgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -67,74 +78,117 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BBBBBB"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BBBBBB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BBBBBB"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
-      </left>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BBBBBB"/>
-      </right>
+      <left/>
+      <right style="thin"/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BBBBBB"/>
-      </right>
+      <left style="thin"/>
+      <right/>
       <top/>
-      <bottom style="thin">
-        <color rgb="00BBBBBB"/>
-      </bottom>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -497,113 +551,439 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>空白敵人角色卡</t>
-        </is>
-      </c>
-    </row>
+          <t>凍結廢土 TRPG — 敵人/威脅 數據卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>欄位</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>內容</t>
-        </is>
-      </c>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>基本資訊</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="11" t="n"/>
+      <c r="D3" s="11" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="12" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr"/>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>敵人名稱</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>類型 (變異生物/環境威脅/NPC)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>類型</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>威脅等級</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr"/>
-    </row>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>威脅等級 (1–5)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>出現於 (凍結區/戰役場次)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>屬性/能力</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr"/>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="12" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>弱點</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr"/>
+      <c r="A8" s="7" t="inlineStr"/>
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="14" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>角色圖</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>【在此貼上角色圖片】</t>
-        </is>
-      </c>
-    </row>
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="16" t="n"/>
+      <c r="F9" s="17" t="n"/>
+    </row>
+    <row r="10"/>
     <row r="11">
-      <c r="B11" s="7" t="n"/>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>屬性</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="12" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="7" t="n"/>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>屬性</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>修正值</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="B13" s="7" t="n"/>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>速度（SPD）</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr"/>
+      <c r="C13" s="6">
+        <f>B13-5</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="B14" s="7" t="n"/>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>知覺（PER）</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr"/>
+      <c r="C14" s="6">
+        <f>B14-5</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" s="8" t="n"/>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>膽量（GUT）</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr"/>
+      <c r="C15" s="6">
+        <f>B15-5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>技術（TEC）</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr"/>
+      <c r="C16" s="6">
+        <f>B16-5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>衍生屬性 (自動計算)</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="12" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>生命值（HP）</t>
+        </is>
+      </c>
+      <c r="B19" s="6">
+        <f>B15*2+10</f>
+        <v/>
+      </c>
+      <c r="C19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>防禦值（AC） (迴避難度)</t>
+        </is>
+      </c>
+      <c r="B20" s="6">
+        <f>10+(B13-5)</f>
+        <v/>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>+ 護甲值 (手動加)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>移動力</t>
+        </is>
+      </c>
+      <c r="B21" s="6">
+        <f>B13+3</f>
+        <v/>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>格/回合</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>先攻修正</t>
+        </is>
+      </c>
+      <c r="B22" s="6">
+        <f>B13-5</f>
+        <v/>
+      </c>
+      <c r="C22" s="9" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>恐慌閾值</t>
+        </is>
+      </c>
+      <c r="B23" s="6">
+        <f>B15*2+5</f>
+        <v/>
+      </c>
+      <c r="C23" s="9" t="inlineStr"/>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>攻擊</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="12" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>攻擊名稱</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>命中公式</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>傷害</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>射程</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>特殊效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr"/>
+      <c r="B27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr"/>
+      <c r="B28" s="6" t="inlineStr"/>
+      <c r="C28" s="6" t="inlineStr"/>
+      <c r="D28" s="6" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr"/>
+      <c r="B29" s="6" t="inlineStr"/>
+      <c r="C29" s="6" t="inlineStr"/>
+      <c r="D29" s="6" t="inlineStr"/>
+      <c r="E29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr"/>
+      <c r="B30" s="6" t="inlineStr"/>
+      <c r="C30" s="6" t="inlineStr"/>
+      <c r="D30" s="6" t="inlineStr"/>
+      <c r="E30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>特殊能力</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="12" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr"/>
+      <c r="B33" s="7" t="inlineStr"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="12" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr"/>
+      <c r="B34" s="7" t="inlineStr"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="12" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr"/>
+      <c r="B35" s="7" t="inlineStr"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="12" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr"/>
+      <c r="B36" s="7" t="inlineStr"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="12" t="n"/>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>時間相關特質 / 戰術行為 / 戰利品</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="12" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr"/>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="12" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr"/>
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="12" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr"/>
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="12" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr"/>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B10:B15"/>
+  <mergeCells count="17">
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A8:F9"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
